--- a/jogos_2025-10-05.xlsx
+++ b/jogos_2025-10-05.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Roasso Kumamoto</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Roasso Kumamoto</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ehime</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mito Hollyhock</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Ehime</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Mito Hollyhock</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8067,10 +8067,10 @@
         <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8196,10 +8196,10 @@
         <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10437,22 +10437,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10695,22 +10695,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,22 +10824,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10953,22 +10953,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,22 +11082,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,22 +11211,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="M85" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="N85" t="n">
-        <v>2.08</v>
+        <v>2.55</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11421,10 +11421,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -11469,22 +11469,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11550,10 +11550,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -11598,22 +11598,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,22 +11856,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,22 +11985,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,22 +12114,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,22 +12501,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,22 +12630,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,22 +12759,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,22 +13017,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z103" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z104" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Slavia Praha II</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Metalist 1925 Kharkiv</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Metalist 1925 Kharkiv</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15162,10 +15162,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15291,10 +15291,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Slavia Praha II</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Metta - LU</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16500,22 +16500,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,13 +16536,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16575,10 +16575,10 @@
         <v>0</v>
       </c>
       <c r="Y125" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z125" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA125" t="n">
         <v>0</v>
@@ -16629,22 +16629,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Metta - LU</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17016,22 +17016,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17274,22 +17274,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,10 +17349,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z131" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17568,13 +17568,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -17607,10 +17607,10 @@
         <v>0</v>
       </c>
       <c r="Y133" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z133" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA133" t="n">
         <v>0</v>
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18445,12 +18445,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18574,12 +18574,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19080,7 +19080,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19090,12 +19090,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19219,12 +19219,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19467,7 +19467,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -19606,12 +19606,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19735,12 +19735,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19854,7 +19854,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19993,12 +19993,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20112,7 +20112,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Hércules CF</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20499,7 +20499,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20509,12 +20509,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20757,7 +20757,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -20767,12 +20767,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20886,7 +20886,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -20896,12 +20896,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21025,12 +21025,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21144,7 +21144,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21154,12 +21154,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21283,12 +21283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21402,7 +21402,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21412,12 +21412,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21531,7 +21531,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21660,7 +21660,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -21670,12 +21670,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21918,7 +21918,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -21928,12 +21928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22047,7 +22047,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22057,12 +22057,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22176,7 +22176,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22186,12 +22186,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22434,7 +22434,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22444,12 +22444,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22563,7 +22563,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -22573,12 +22573,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22821,7 +22821,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -23079,7 +23079,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23089,12 +23089,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Hércules CF</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23208,7 +23208,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23337,7 +23337,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -23347,12 +23347,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23466,7 +23466,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23595,7 +23595,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -23605,12 +23605,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -23734,12 +23734,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23853,7 +23853,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24111,7 +24111,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24756,7 +24756,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -24766,12 +24766,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24895,12 +24895,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25014,7 +25014,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25024,12 +25024,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25143,7 +25143,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -25153,12 +25153,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25272,7 +25272,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25282,12 +25282,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25401,7 +25401,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25411,12 +25411,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -25530,7 +25530,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -25540,12 +25540,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -25669,12 +25669,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -25788,7 +25788,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -25798,12 +25798,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26046,7 +26046,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26175,7 +26175,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26304,7 +26304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26314,12 +26314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26443,12 +26443,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26691,22 +26691,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26820,22 +26820,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26949,7 +26949,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -26959,12 +26959,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -26985,13 +26985,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M206" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N206" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -27024,10 +27024,10 @@
         <v>0</v>
       </c>
       <c r="Y206" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z206" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA206" t="n">
         <v>0</v>
@@ -27078,7 +27078,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27088,12 +27088,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27114,13 +27114,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N207" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -27153,10 +27153,10 @@
         <v>0</v>
       </c>
       <c r="Y207" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z207" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA207" t="n">
         <v>0</v>
@@ -27207,22 +27207,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27336,22 +27336,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27852,22 +27852,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27981,22 +27981,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28239,7 +28239,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28249,12 +28249,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28275,13 +28275,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M216" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="N216" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -28320,10 +28320,10 @@
         <v>0</v>
       </c>
       <c r="AA216" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB216" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC216" t="n">
         <v>0</v>
@@ -28368,7 +28368,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -28378,12 +28378,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -28404,13 +28404,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="N217" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -28449,10 +28449,10 @@
         <v>0</v>
       </c>
       <c r="AA217" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB217" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC217" t="n">
         <v>0</v>
@@ -28497,7 +28497,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -28507,12 +28507,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -28626,7 +28626,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -28636,12 +28636,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -28755,22 +28755,22 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -28884,22 +28884,22 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -29013,7 +29013,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29049,13 +29049,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N222" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29088,10 +29088,10 @@
         <v>0</v>
       </c>
       <c r="Y222" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z222" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA222" t="n">
         <v>0</v>
@@ -29142,7 +29142,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29400,22 +29400,22 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -29539,12 +29539,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29658,7 +29658,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -29668,12 +29668,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -29787,7 +29787,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -29797,12 +29797,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -29926,12 +29926,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30045,7 +30045,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -30055,12 +30055,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30081,13 +30081,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M230" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="N230" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -30120,10 +30120,10 @@
         <v>0</v>
       </c>
       <c r="Y230" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z230" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA230" t="n">
         <v>0</v>
@@ -30174,7 +30174,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -30184,12 +30184,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30432,7 +30432,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -30442,12 +30442,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -30561,7 +30561,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -30571,12 +30571,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -30597,13 +30597,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M234" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N234" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -30636,10 +30636,10 @@
         <v>0</v>
       </c>
       <c r="Y234" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z234" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA234" t="n">
         <v>0</v>
@@ -30690,7 +30690,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -30700,12 +30700,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30829,12 +30829,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30948,7 +30948,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -30958,12 +30958,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31077,22 +31077,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31335,22 +31335,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31371,13 +31371,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M240" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N240" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -31410,10 +31410,10 @@
         <v>0</v>
       </c>
       <c r="Y240" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z240" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA240" t="n">
         <v>0</v>
@@ -31464,22 +31464,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -31593,22 +31593,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -31629,13 +31629,13 @@
         </is>
       </c>
       <c r="L242" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M242" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N242" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O242" t="n">
         <v>0</v>
@@ -31668,10 +31668,10 @@
         <v>0</v>
       </c>
       <c r="Y242" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z242" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA242" t="n">
         <v>0</v>
@@ -31722,7 +31722,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -31732,12 +31732,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -31851,22 +31851,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -31990,12 +31990,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32109,7 +32109,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -32119,12 +32119,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32238,7 +32238,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -32248,12 +32248,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32367,7 +32367,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -32377,12 +32377,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -32496,7 +32496,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -32506,12 +32506,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32625,7 +32625,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -32635,12 +32635,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32754,7 +32754,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -32764,12 +32764,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -32790,13 +32790,13 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M251" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="N251" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O251" t="n">
         <v>0</v>
@@ -32829,10 +32829,10 @@
         <v>0</v>
       </c>
       <c r="Y251" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z251" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA251" t="n">
         <v>0</v>
@@ -32883,22 +32883,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -33012,22 +33012,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33151,12 +33151,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -33177,13 +33177,13 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="M254" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="N254" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="O254" t="n">
         <v>0</v>
@@ -33216,16 +33216,16 @@
         <v>0</v>
       </c>
       <c r="Y254" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z254" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA254" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB254" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC254" t="n">
         <v>0</v>
@@ -33270,7 +33270,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -33280,12 +33280,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="L255" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M255" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N255" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O255" t="n">
         <v>0</v>
@@ -33345,10 +33345,10 @@
         <v>0</v>
       </c>
       <c r="Y255" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z255" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA255" t="n">
         <v>0</v>
@@ -33409,12 +33409,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33435,13 +33435,13 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>1.65</v>
+        <v>3.15</v>
       </c>
       <c r="M256" t="n">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="N256" t="n">
-        <v>4.7</v>
+        <v>2.25</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -33474,16 +33474,16 @@
         <v>0</v>
       </c>
       <c r="Y256" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z256" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA256" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB256" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC256" t="n">
         <v>0</v>
@@ -33528,7 +33528,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -33538,12 +33538,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -33564,13 +33564,13 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M257" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N257" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -33603,10 +33603,10 @@
         <v>0</v>
       </c>
       <c r="Y257" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z257" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA257" t="n">
         <v>0</v>
@@ -33657,7 +33657,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -33667,12 +33667,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33915,7 +33915,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -33925,12 +33925,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -34044,7 +34044,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -34054,12 +34054,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34173,7 +34173,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -34183,12 +34183,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34302,7 +34302,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -34312,12 +34312,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -34431,7 +34431,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -34441,12 +34441,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -34689,7 +34689,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -34699,12 +34699,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -34818,7 +34818,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -34828,12 +34828,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -34947,7 +34947,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -34957,12 +34957,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -35076,7 +35076,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -35086,12 +35086,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -35205,7 +35205,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -35215,12 +35215,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -35334,7 +35334,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -35344,12 +35344,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -35463,7 +35463,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -35473,12 +35473,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -35592,7 +35592,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -35602,12 +35602,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -35721,7 +35721,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -35731,12 +35731,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -35850,7 +35850,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -35860,12 +35860,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -35979,7 +35979,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -35989,12 +35989,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -36015,13 +36015,13 @@
         </is>
       </c>
       <c r="L276" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M276" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N276" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O276" t="n">
         <v>0</v>
@@ -36054,10 +36054,10 @@
         <v>0</v>
       </c>
       <c r="Y276" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Z276" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA276" t="n">
         <v>0</v>
@@ -36108,7 +36108,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -36118,12 +36118,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -36237,7 +36237,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -36247,12 +36247,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -36376,12 +36376,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -36495,7 +36495,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -36505,12 +36505,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -36753,7 +36753,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -36763,12 +36763,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -36789,13 +36789,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M282" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N282" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -36828,10 +36828,10 @@
         <v>0</v>
       </c>
       <c r="Y282" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z282" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA282" t="n">
         <v>0</v>
@@ -36882,7 +36882,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -36892,12 +36892,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -37011,7 +37011,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -37021,12 +37021,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -37785,7 +37785,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -37795,12 +37795,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -37914,22 +37914,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -38053,12 +38053,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -38172,22 +38172,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -38430,22 +38430,22 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -38559,7 +38559,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -38569,12 +38569,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -38688,22 +38688,22 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -38956,12 +38956,12 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -39075,22 +39075,22 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -39204,22 +39204,22 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -39343,12 +39343,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -39462,22 +39462,22 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -39591,22 +39591,22 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -39720,22 +39720,22 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -39978,7 +39978,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -39988,12 +39988,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -40107,7 +40107,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -40117,12 +40117,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -40236,22 +40236,22 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -40365,7 +40365,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -40504,12 +40504,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -40623,22 +40623,22 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Rosenborg</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -40659,13 +40659,13 @@
         </is>
       </c>
       <c r="L312" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M312" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N312" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O312" t="n">
         <v>0</v>
@@ -40698,10 +40698,10 @@
         <v>0</v>
       </c>
       <c r="Y312" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z312" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA312" t="n">
         <v>0</v>
@@ -40752,22 +40752,22 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Rosenborg</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -40788,13 +40788,13 @@
         </is>
       </c>
       <c r="L313" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M313" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N313" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O313" t="n">
         <v>0</v>
@@ -40827,10 +40827,10 @@
         <v>0</v>
       </c>
       <c r="Y313" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z313" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA313" t="n">
         <v>0</v>
@@ -40881,7 +40881,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -40891,12 +40891,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -41010,7 +41010,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -41020,12 +41020,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -41046,13 +41046,13 @@
         </is>
       </c>
       <c r="L315" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M315" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N315" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O315" t="n">
         <v>0</v>
@@ -41085,10 +41085,10 @@
         <v>0</v>
       </c>
       <c r="Y315" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z315" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA315" t="n">
         <v>0</v>
@@ -41139,7 +41139,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -41149,12 +41149,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -41175,13 +41175,13 @@
         </is>
       </c>
       <c r="L316" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M316" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N316" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O316" t="n">
         <v>0</v>
@@ -41214,10 +41214,10 @@
         <v>0</v>
       </c>
       <c r="Y316" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z316" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA316" t="n">
         <v>0</v>
@@ -41268,7 +41268,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -41278,12 +41278,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -41304,13 +41304,13 @@
         </is>
       </c>
       <c r="L317" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M317" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N317" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O317" t="n">
         <v>0</v>
@@ -41343,10 +41343,10 @@
         <v>0</v>
       </c>
       <c r="Y317" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z317" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA317" t="n">
         <v>0</v>
@@ -41397,7 +41397,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -41407,12 +41407,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G318" t="n">
@@ -41433,13 +41433,13 @@
         </is>
       </c>
       <c r="L318" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M318" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N318" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O318" t="n">
         <v>0</v>
@@ -41472,10 +41472,10 @@
         <v>0</v>
       </c>
       <c r="Y318" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z318" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA318" t="n">
         <v>0</v>
@@ -41913,7 +41913,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -41923,12 +41923,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -41949,13 +41949,13 @@
         </is>
       </c>
       <c r="L322" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M322" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N322" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="O322" t="n">
         <v>0</v>
@@ -41988,10 +41988,10 @@
         <v>0</v>
       </c>
       <c r="Y322" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z322" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA322" t="n">
         <v>0</v>
@@ -42171,7 +42171,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -42181,12 +42181,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G324" t="n">
@@ -42300,7 +42300,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -42310,12 +42310,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -42429,7 +42429,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -42439,12 +42439,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G326" t="n">
@@ -42558,7 +42558,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -42568,12 +42568,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G327" t="n">
@@ -42687,7 +42687,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -42697,12 +42697,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="G328" t="n">
@@ -42723,13 +42723,13 @@
         </is>
       </c>
       <c r="L328" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M328" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N328" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="O328" t="n">
         <v>0</v>
@@ -42762,10 +42762,10 @@
         <v>0</v>
       </c>
       <c r="Y328" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z328" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA328" t="n">
         <v>0</v>
@@ -42816,7 +42816,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -42826,12 +42826,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G329" t="n">
@@ -42852,13 +42852,13 @@
         </is>
       </c>
       <c r="L329" t="n">
-        <v>4.8</v>
+        <v>2.35</v>
       </c>
       <c r="M329" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="N329" t="n">
-        <v>1.65</v>
+        <v>3.15</v>
       </c>
       <c r="O329" t="n">
         <v>0</v>
@@ -42891,16 +42891,16 @@
         <v>0</v>
       </c>
       <c r="Y329" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z329" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA329" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB329" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC329" t="n">
         <v>0</v>
@@ -42945,7 +42945,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -42955,12 +42955,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G330" t="n">
@@ -42981,13 +42981,13 @@
         </is>
       </c>
       <c r="L330" t="n">
-        <v>2.35</v>
+        <v>4.8</v>
       </c>
       <c r="M330" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="N330" t="n">
-        <v>3.15</v>
+        <v>1.65</v>
       </c>
       <c r="O330" t="n">
         <v>0</v>
@@ -43020,16 +43020,16 @@
         <v>0</v>
       </c>
       <c r="Y330" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z330" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA330" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB330" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC330" t="n">
         <v>0</v>
@@ -43074,7 +43074,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -43084,12 +43084,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G331" t="n">
@@ -43461,22 +43461,22 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G334" t="n">
@@ -43590,22 +43590,22 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G335" t="n">
@@ -43719,22 +43719,22 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G336" t="n">
@@ -43848,7 +43848,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -43858,12 +43858,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G337" t="n">
@@ -43977,22 +43977,22 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G338" t="n">
@@ -44364,7 +44364,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -44374,12 +44374,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G341" t="n">
@@ -44493,7 +44493,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -44503,12 +44503,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G342" t="n">
@@ -44622,7 +44622,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -44632,12 +44632,12 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G343" t="n">
@@ -44761,12 +44761,12 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G344" t="n">
@@ -44890,12 +44890,12 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G345" t="n">
@@ -45019,12 +45019,12 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G346" t="n">
@@ -45148,12 +45148,12 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G347" t="n">
@@ -45267,7 +45267,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -45277,12 +45277,12 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G348" t="n">
@@ -45793,12 +45793,12 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G352" t="n">
@@ -45922,12 +45922,12 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G353" t="n">
@@ -46180,12 +46180,12 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G355" t="n">
@@ -46309,12 +46309,12 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G356" t="n">
@@ -46438,12 +46438,12 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G357" t="n">
@@ -47212,12 +47212,12 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G363" t="n">
@@ -47341,12 +47341,12 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G364" t="n">

--- a/jogos_2025-10-05.xlsx
+++ b/jogos_2025-10-05.xlsx
@@ -633,22 +633,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Renofa Yamaguchi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Renofa Yamaguchi</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Roasso Kumamoto</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Roasso Kumamoto</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Orenburg</t>
+          <t>Imigresen</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Imigresen</t>
+          <t>Orenburg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,22 +9534,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,22 +9792,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10131,10 +10131,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -10179,22 +10179,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="M78" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="N78" t="n">
-        <v>2.08</v>
+        <v>2.65</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10695,22 +10695,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.24</v>
+        <v>3.4</v>
       </c>
       <c r="M81" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N81" t="n">
-        <v>3</v>
+        <v>2.02</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11034,10 +11034,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -11082,22 +11082,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,22 +11340,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11421,10 +11421,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -11469,22 +11469,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,22 +11856,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12114,22 +12114,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,22 +12372,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,22 +12501,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,22 +12759,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,22 +12888,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>3.45</v>
+        <v>1.35</v>
       </c>
       <c r="M104" t="n">
-        <v>3.15</v>
+        <v>4.9</v>
       </c>
       <c r="N104" t="n">
-        <v>2.25</v>
+        <v>7.2</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>2.35</v>
+        <v>1.62</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Metalist 1925 Kharkiv</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14775,10 +14775,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Slavia Praha II</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Metalist 1925 Kharkiv</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15162,10 +15162,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Slavia Praha II</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Metta - LU</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16500,22 +16500,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16629,22 +16629,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16758,22 +16758,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z127" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17016,22 +17016,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Metta - LU</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17145,22 +17145,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="M131" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="N131" t="n">
-        <v>6.1</v>
+        <v>4.2</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,10 +17349,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="Z131" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z132" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>
@@ -17532,22 +17532,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17568,13 +17568,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -17607,10 +17607,10 @@
         <v>0</v>
       </c>
       <c r="Y133" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z133" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA133" t="n">
         <v>0</v>
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,22 +17790,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18445,12 +18445,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18574,12 +18574,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18600,13 +18600,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M141" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -18639,10 +18639,10 @@
         <v>0</v>
       </c>
       <c r="Y141" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z141" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA141" t="n">
         <v>0</v>
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18822,7 +18822,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -18832,12 +18832,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19080,7 +19080,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19090,12 +19090,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19467,7 +19467,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19606,12 +19606,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -19735,12 +19735,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19854,7 +19854,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19993,12 +19993,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20509,12 +20509,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -20638,12 +20638,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20757,7 +20757,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -20767,12 +20767,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20886,7 +20886,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -20896,12 +20896,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21025,12 +21025,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21154,12 +21154,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21283,12 +21283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21412,12 +21412,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21670,12 +21670,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21928,12 +21928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22047,7 +22047,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22057,12 +22057,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22176,7 +22176,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22186,12 +22186,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22434,7 +22434,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22444,12 +22444,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22563,7 +22563,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -22573,12 +22573,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22821,7 +22821,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -22950,7 +22950,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -22960,12 +22960,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23079,7 +23079,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23089,12 +23089,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Hércules CF</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23337,7 +23337,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -23347,12 +23347,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23595,7 +23595,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -23605,12 +23605,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23734,12 +23734,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24121,12 +24121,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24369,7 +24369,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24756,7 +24756,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -24766,12 +24766,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -25143,7 +25143,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -25153,12 +25153,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25272,7 +25272,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25282,12 +25282,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25411,12 +25411,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -25530,7 +25530,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -25540,12 +25540,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -25669,12 +25669,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -25788,7 +25788,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -25798,12 +25798,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Hércules CF</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26046,7 +26046,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26175,7 +26175,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26304,7 +26304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26314,12 +26314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26433,7 +26433,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -26443,12 +26443,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26691,22 +26691,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26820,22 +26820,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26949,7 +26949,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -26959,12 +26959,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -26985,13 +26985,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M206" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N206" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -27024,10 +27024,10 @@
         <v>0</v>
       </c>
       <c r="Y206" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z206" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA206" t="n">
         <v>0</v>
@@ -27078,7 +27078,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27088,12 +27088,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27207,22 +27207,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27346,12 +27346,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27372,13 +27372,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M209" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N209" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -27411,10 +27411,10 @@
         <v>0</v>
       </c>
       <c r="Y209" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z209" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA209" t="n">
         <v>0</v>
@@ -27594,22 +27594,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27723,7 +27723,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -27733,12 +27733,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27852,22 +27852,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27981,22 +27981,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28110,7 +28110,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28120,12 +28120,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28146,13 +28146,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M215" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N215" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -28191,10 +28191,10 @@
         <v>0</v>
       </c>
       <c r="AA215" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB215" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC215" t="n">
         <v>0</v>
@@ -28368,7 +28368,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -28378,12 +28378,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -28497,7 +28497,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -28507,12 +28507,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -28533,13 +28533,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M218" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -28578,10 +28578,10 @@
         <v>0</v>
       </c>
       <c r="AA218" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB218" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC218" t="n">
         <v>0</v>
@@ -28636,12 +28636,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -28755,7 +28755,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -28884,7 +28884,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -28894,12 +28894,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -29013,7 +29013,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29049,13 +29049,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M222" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N222" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29088,10 +29088,10 @@
         <v>0</v>
       </c>
       <c r="Y222" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z222" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA222" t="n">
         <v>0</v>
@@ -29142,7 +29142,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29400,22 +29400,22 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -29539,12 +29539,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29658,7 +29658,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -29668,12 +29668,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -29787,7 +29787,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -29797,12 +29797,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -29916,7 +29916,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -29926,12 +29926,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30045,7 +30045,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -30055,12 +30055,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30174,7 +30174,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -30184,12 +30184,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30432,22 +30432,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -30561,7 +30561,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -30571,12 +30571,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -30597,13 +30597,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M234" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N234" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -30636,10 +30636,10 @@
         <v>0</v>
       </c>
       <c r="Y234" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z234" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA234" t="n">
         <v>0</v>
@@ -30819,7 +30819,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -30829,12 +30829,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30948,7 +30948,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -30958,12 +30958,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31077,22 +31077,22 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31345,12 +31345,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31371,13 +31371,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>1.88</v>
+        <v>16</v>
       </c>
       <c r="M240" t="n">
-        <v>3.3</v>
+        <v>7.9</v>
       </c>
       <c r="N240" t="n">
-        <v>4.6</v>
+        <v>1.16</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -31410,10 +31410,10 @@
         <v>0</v>
       </c>
       <c r="Y240" t="n">
-        <v>2.45</v>
+        <v>1.62</v>
       </c>
       <c r="Z240" t="n">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="AA240" t="n">
         <v>0</v>
@@ -31474,12 +31474,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -31722,22 +31722,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -31851,7 +31851,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -31861,12 +31861,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -31980,7 +31980,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -31990,12 +31990,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32109,7 +32109,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -32119,12 +32119,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32238,7 +32238,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -32248,12 +32248,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32367,7 +32367,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -32377,12 +32377,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -32496,7 +32496,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -32506,12 +32506,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32625,7 +32625,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -32635,12 +32635,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32661,13 +32661,13 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M250" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N250" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -32700,10 +32700,10 @@
         <v>0</v>
       </c>
       <c r="Y250" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z250" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA250" t="n">
         <v>0</v>
@@ -32754,7 +32754,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -32764,12 +32764,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -32790,13 +32790,13 @@
         </is>
       </c>
       <c r="L251" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M251" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="N251" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="O251" t="n">
         <v>0</v>
@@ -32829,10 +32829,10 @@
         <v>0</v>
       </c>
       <c r="Y251" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z251" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA251" t="n">
         <v>0</v>
@@ -32883,22 +32883,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -33012,22 +33012,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33141,7 +33141,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -33151,12 +33151,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -33177,13 +33177,13 @@
         </is>
       </c>
       <c r="L254" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M254" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N254" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O254" t="n">
         <v>0</v>
@@ -33222,10 +33222,10 @@
         <v>0</v>
       </c>
       <c r="AA254" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB254" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC254" t="n">
         <v>0</v>
@@ -33280,12 +33280,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="L255" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="M255" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="N255" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="O255" t="n">
         <v>0</v>
@@ -33345,16 +33345,16 @@
         <v>0</v>
       </c>
       <c r="Y255" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z255" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA255" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB255" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC255" t="n">
         <v>0</v>
@@ -33399,7 +33399,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -33409,12 +33409,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33435,13 +33435,13 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M256" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N256" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -33474,10 +33474,10 @@
         <v>0</v>
       </c>
       <c r="Y256" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z256" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA256" t="n">
         <v>0</v>
@@ -33528,7 +33528,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -33538,12 +33538,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -33564,13 +33564,13 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M257" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N257" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -33603,10 +33603,10 @@
         <v>0</v>
       </c>
       <c r="Y257" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z257" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA257" t="n">
         <v>0</v>
@@ -33657,7 +33657,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -33667,12 +33667,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33693,13 +33693,13 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M258" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N258" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -33732,10 +33732,10 @@
         <v>0</v>
       </c>
       <c r="Y258" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z258" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA258" t="n">
         <v>0</v>
@@ -33915,7 +33915,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -33925,12 +33925,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -34044,7 +34044,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -34054,12 +34054,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34173,7 +34173,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -34183,12 +34183,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34312,12 +34312,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -34431,7 +34431,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -34441,12 +34441,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -34560,22 +34560,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -34596,13 +34596,13 @@
         </is>
       </c>
       <c r="L265" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M265" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N265" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O265" t="n">
         <v>0</v>
@@ -34689,7 +34689,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -34699,12 +34699,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Lech Poznań</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -34818,7 +34818,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -34828,12 +34828,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Lech Poznań</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -34947,22 +34947,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -34983,13 +34983,13 @@
         </is>
       </c>
       <c r="L268" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M268" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N268" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O268" t="n">
         <v>0</v>
@@ -35076,7 +35076,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -35086,12 +35086,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -35205,7 +35205,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -35215,12 +35215,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -35241,13 +35241,13 @@
         </is>
       </c>
       <c r="L270" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M270" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N270" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O270" t="n">
         <v>0</v>
@@ -35280,10 +35280,10 @@
         <v>0</v>
       </c>
       <c r="Y270" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z270" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA270" t="n">
         <v>0</v>
@@ -35334,7 +35334,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -35344,12 +35344,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -35463,7 +35463,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -35473,12 +35473,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -35850,7 +35850,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -35860,12 +35860,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -35979,7 +35979,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -35989,12 +35989,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -36108,7 +36108,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -36118,12 +36118,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -36144,13 +36144,13 @@
         </is>
       </c>
       <c r="L277" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M277" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N277" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O277" t="n">
         <v>0</v>
@@ -36183,10 +36183,10 @@
         <v>0</v>
       </c>
       <c r="Y277" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z277" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA277" t="n">
         <v>0</v>
@@ -36237,7 +36237,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -36247,12 +36247,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -36366,7 +36366,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -36376,12 +36376,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -36495,7 +36495,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -36505,12 +36505,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -36624,7 +36624,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -36634,12 +36634,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -36753,7 +36753,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -36763,12 +36763,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -36789,13 +36789,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M282" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N282" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -36828,10 +36828,10 @@
         <v>0</v>
       </c>
       <c r="Y282" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Z282" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA282" t="n">
         <v>0</v>
@@ -36882,7 +36882,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -36892,12 +36892,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -37537,12 +37537,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -37656,7 +37656,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -37666,12 +37666,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -37785,22 +37785,22 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -37914,7 +37914,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -37924,12 +37924,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -38172,22 +38172,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -38440,12 +38440,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -38559,22 +38559,22 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -38688,22 +38688,22 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -38817,22 +38817,22 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -38853,13 +38853,13 @@
         </is>
       </c>
       <c r="L298" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M298" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N298" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O298" t="n">
         <v>0</v>
@@ -38892,10 +38892,10 @@
         <v>0</v>
       </c>
       <c r="Y298" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z298" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA298" t="n">
         <v>0</v>
@@ -38946,22 +38946,22 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -39075,22 +39075,22 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -39204,22 +39204,22 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -39333,22 +39333,22 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -39462,22 +39462,22 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -39591,22 +39591,22 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -39730,12 +39730,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -39849,7 +39849,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -39859,12 +39859,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -39978,7 +39978,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -39988,12 +39988,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -40117,12 +40117,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -40236,22 +40236,22 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -40365,22 +40365,22 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -40494,22 +40494,22 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -40891,12 +40891,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -40917,13 +40917,13 @@
         </is>
       </c>
       <c r="L314" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M314" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N314" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O314" t="n">
         <v>0</v>
@@ -40956,10 +40956,10 @@
         <v>0</v>
       </c>
       <c r="Y314" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z314" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA314" t="n">
         <v>0</v>
@@ -41010,7 +41010,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -41020,12 +41020,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -41046,13 +41046,13 @@
         </is>
       </c>
       <c r="L315" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M315" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N315" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O315" t="n">
         <v>0</v>
@@ -41085,10 +41085,10 @@
         <v>0</v>
       </c>
       <c r="Y315" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z315" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA315" t="n">
         <v>0</v>
@@ -41139,7 +41139,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -41149,12 +41149,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -41175,13 +41175,13 @@
         </is>
       </c>
       <c r="L316" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M316" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N316" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O316" t="n">
         <v>0</v>
@@ -41214,10 +41214,10 @@
         <v>0</v>
       </c>
       <c r="Y316" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z316" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA316" t="n">
         <v>0</v>
@@ -41397,7 +41397,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -41407,12 +41407,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G318" t="n">
@@ -41433,13 +41433,13 @@
         </is>
       </c>
       <c r="L318" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M318" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N318" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O318" t="n">
         <v>0</v>
@@ -41472,10 +41472,10 @@
         <v>0</v>
       </c>
       <c r="Y318" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z318" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA318" t="n">
         <v>0</v>
@@ -41526,22 +41526,22 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -41562,13 +41562,13 @@
         </is>
       </c>
       <c r="L319" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M319" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N319" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O319" t="n">
         <v>0</v>
@@ -41655,22 +41655,22 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G320" t="n">
@@ -41691,13 +41691,13 @@
         </is>
       </c>
       <c r="L320" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M320" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N320" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O320" t="n">
         <v>0</v>
@@ -41794,12 +41794,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G321" t="n">
@@ -41823,10 +41823,10 @@
         <v>2.63</v>
       </c>
       <c r="M321" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N321" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="O321" t="n">
         <v>0</v>
@@ -41913,7 +41913,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -41923,12 +41923,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -41949,13 +41949,13 @@
         </is>
       </c>
       <c r="L322" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M322" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N322" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="O322" t="n">
         <v>0</v>
@@ -41988,10 +41988,10 @@
         <v>0</v>
       </c>
       <c r="Y322" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z322" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA322" t="n">
         <v>0</v>
@@ -42042,7 +42042,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -42052,12 +42052,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G323" t="n">
@@ -42171,7 +42171,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -42181,12 +42181,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G324" t="n">
@@ -42207,13 +42207,13 @@
         </is>
       </c>
       <c r="L324" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M324" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N324" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="O324" t="n">
         <v>0</v>
@@ -42246,10 +42246,10 @@
         <v>0</v>
       </c>
       <c r="Y324" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z324" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA324" t="n">
         <v>0</v>
@@ -42300,7 +42300,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -42310,12 +42310,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -42429,7 +42429,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -42439,12 +42439,12 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G326" t="n">
@@ -42558,7 +42558,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -42568,12 +42568,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G327" t="n">
@@ -42687,7 +42687,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -42697,12 +42697,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G328" t="n">
@@ -42816,7 +42816,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -42826,12 +42826,12 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G329" t="n">
@@ -42852,13 +42852,13 @@
         </is>
       </c>
       <c r="L329" t="n">
-        <v>2.35</v>
+        <v>4.8</v>
       </c>
       <c r="M329" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="N329" t="n">
-        <v>3.15</v>
+        <v>1.65</v>
       </c>
       <c r="O329" t="n">
         <v>0</v>
@@ -42891,16 +42891,16 @@
         <v>0</v>
       </c>
       <c r="Y329" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z329" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA329" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB329" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC329" t="n">
         <v>0</v>
@@ -42945,7 +42945,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -42955,12 +42955,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G330" t="n">
@@ -42981,13 +42981,13 @@
         </is>
       </c>
       <c r="L330" t="n">
-        <v>4.8</v>
+        <v>2.35</v>
       </c>
       <c r="M330" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="N330" t="n">
-        <v>1.65</v>
+        <v>3.15</v>
       </c>
       <c r="O330" t="n">
         <v>0</v>
@@ -43020,16 +43020,16 @@
         <v>0</v>
       </c>
       <c r="Y330" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z330" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA330" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB330" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC330" t="n">
         <v>0</v>
@@ -43074,7 +43074,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -43084,12 +43084,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G331" t="n">
@@ -43203,22 +43203,22 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G332" t="n">
@@ -43332,7 +43332,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -43342,12 +43342,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Tusker</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G333" t="n">
@@ -43461,7 +43461,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -43471,12 +43471,12 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Tusker</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="G334" t="n">
@@ -43590,22 +43590,22 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G335" t="n">
@@ -43626,13 +43626,13 @@
         </is>
       </c>
       <c r="L335" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M335" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N335" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O335" t="n">
         <v>0</v>
@@ -43665,10 +43665,10 @@
         <v>0</v>
       </c>
       <c r="Y335" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z335" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA335" t="n">
         <v>0</v>
@@ -43729,12 +43729,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G336" t="n">
@@ -43848,22 +43848,22 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G337" t="n">
@@ -43977,22 +43977,22 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G338" t="n">
@@ -44364,7 +44364,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -44374,12 +44374,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G341" t="n">
@@ -44493,7 +44493,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -44503,12 +44503,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G342" t="n">
@@ -44632,12 +44632,12 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="G343" t="n">
@@ -44751,7 +44751,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -44761,12 +44761,12 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G344" t="n">
@@ -45277,12 +45277,12 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G348" t="n">
@@ -45396,7 +45396,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -45406,12 +45406,12 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G349" t="n">
@@ -45535,12 +45535,12 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G350" t="n">
@@ -45664,12 +45664,12 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G351" t="n">
@@ -45793,12 +45793,12 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G352" t="n">
@@ -45912,22 +45912,22 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G353" t="n">
@@ -45948,13 +45948,13 @@
         </is>
       </c>
       <c r="L353" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M353" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N353" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O353" t="n">
         <v>0</v>
@@ -45987,10 +45987,10 @@
         <v>0</v>
       </c>
       <c r="Y353" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z353" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA353" t="n">
         <v>0</v>
@@ -46041,22 +46041,22 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G354" t="n">
@@ -46077,13 +46077,13 @@
         </is>
       </c>
       <c r="L354" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M354" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N354" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O354" t="n">
         <v>0</v>
@@ -46116,10 +46116,10 @@
         <v>0</v>
       </c>
       <c r="Y354" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z354" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA354" t="n">
         <v>0</v>
@@ -46180,12 +46180,12 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G355" t="n">
@@ -46309,12 +46309,12 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G356" t="n">
@@ -46696,12 +46696,12 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G359" t="n">
@@ -46825,12 +46825,12 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="G360" t="n">
@@ -47212,12 +47212,12 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G363" t="n">
@@ -47341,12 +47341,12 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G364" t="n">

--- a/jogos_2025-10-05.xlsx
+++ b/jogos_2025-10-05.xlsx
@@ -633,22 +633,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Renofa Yamaguchi</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sagan Tosu</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Daejeon Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Blaublitz Akita</t>
+          <t>Tokushima Vortis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tokushima Vortis</t>
+          <t>Blaublitz Akita</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Renofa Yamaguchi</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Sagan Tosu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Daejeon Citizen</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kashima Antlers</t>
+          <t>Roasso Kumamoto</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gamba Osaka</t>
+          <t>Iwaki</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Roasso Kumamoto</t>
+          <t>Kashima Antlers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Iwaki</t>
+          <t>Gamba Osaka</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Chrudim</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Chrudim</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9186,10 +9186,10 @@
         <v>2.6</v>
       </c>
       <c r="M68" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="N68" t="n">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9534,22 +9534,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,22 +10050,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="M78" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="N78" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,16 +10512,16 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10824,22 +10824,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Magdeburg</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10905,10 +10905,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10953,22 +10953,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,22 +11211,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11340,22 +11340,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11469,22 +11469,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,22 +11598,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>3.45</v>
+        <v>2.08</v>
       </c>
       <c r="M88" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N88" t="n">
-        <v>2.25</v>
+        <v>3.6</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>2.35</v>
+        <v>1.88</v>
       </c>
       <c r="Z88" t="n">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.55</v>
+        <v>3.45</v>
       </c>
       <c r="M89" t="n">
-        <v>4.17</v>
+        <v>3.15</v>
       </c>
       <c r="N89" t="n">
-        <v>4.53</v>
+        <v>2.25</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,22 +12243,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nordsjælland</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,22 +12372,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,22 +12501,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Randers</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Viborg</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Lausanne Sport</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.08</v>
+        <v>1.55</v>
       </c>
       <c r="M97" t="n">
-        <v>3.4</v>
+        <v>4.17</v>
       </c>
       <c r="N97" t="n">
-        <v>3.6</v>
+        <v>4.53</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Lausanne Sport</t>
+          <t>Randers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Viborg</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Nordsjælland</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>PSM</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>PSM</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Dynamo Kyiv</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Metalist 1925 Kharkiv</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Slavia Praha II</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14775,10 +14775,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Slavia Praha II</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15291,10 +15291,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Dynamo Kyiv</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Metalist 1925 Kharkiv</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>PDRM</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Johor Darul Ta'zim</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z122" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z123" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16371,22 +16371,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z124" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16500,22 +16500,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,13 +16536,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16575,10 +16575,10 @@
         <v>0</v>
       </c>
       <c r="Y125" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z125" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA125" t="n">
         <v>0</v>
@@ -16629,22 +16629,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16887,22 +16887,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>PDRM</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Johor Darul Ta'zim</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17016,22 +17016,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17145,22 +17145,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17274,22 +17274,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z132" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Metta - LU</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,22 +17919,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Metta - LU</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -17955,13 +17955,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -17994,10 +17994,10 @@
         <v>0</v>
       </c>
       <c r="Y136" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z136" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA136" t="n">
         <v>0</v>
@@ -18048,7 +18048,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18058,12 +18058,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18084,13 +18084,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>2.3</v>
+        <v>1.78</v>
       </c>
       <c r="M137" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="N137" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -18123,10 +18123,10 @@
         <v>0</v>
       </c>
       <c r="Y137" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="Z137" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AA137" t="n">
         <v>0</v>
@@ -18177,22 +18177,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18213,13 +18213,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -18252,10 +18252,10 @@
         <v>0</v>
       </c>
       <c r="Y138" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z138" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA138" t="n">
         <v>0</v>
@@ -18342,13 +18342,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -18822,7 +18822,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -18832,12 +18832,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18858,13 +18858,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -18897,10 +18897,10 @@
         <v>0</v>
       </c>
       <c r="Y143" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z143" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA143" t="n">
         <v>0</v>
@@ -18951,7 +18951,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -19080,7 +19080,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19090,12 +19090,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19219,12 +19219,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>UN Käerjéng</t>
+          <t>Victoria Rosport</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Hostert</t>
+          <t>Rodange</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Gazişehir Gaziantep</t>
+          <t>Hércules CF</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>UT Pétange</t>
+          <t>UN Käerjéng</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Hostert</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -19606,12 +19606,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19735,12 +19735,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19854,7 +19854,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>UT Pétange</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19983,7 +19983,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -19993,12 +19993,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Progrès Niederkorn</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Atert Bissen</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20112,7 +20112,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>UNA Strassen</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Mamer</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Swift Hesperange</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Jeunesse Canach</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>F91 Dudelange</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Jeunesse d'Esch</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20509,12 +20509,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20628,7 +20628,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -20638,12 +20638,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Lusitano Évora 1911</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20757,7 +20757,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -20767,12 +20767,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20886,7 +20886,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -20896,12 +20896,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21015,7 +21015,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21025,12 +21025,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21144,7 +21144,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21154,12 +21154,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21283,12 +21283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Victoria Rosport</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Rodange</t>
+          <t>Gazişehir Gaziantep</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21412,12 +21412,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21531,7 +21531,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Swift Hesperange</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Jeunesse Canach</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21670,12 +21670,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Mondorf-les-Bains</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21928,12 +21928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -22057,12 +22057,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22186,12 +22186,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22305,7 +22305,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Progrès Niederkorn</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Atert Bissen</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22434,7 +22434,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22444,12 +22444,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Sanjoanense</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>F91 Dudelange</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Jeunesse d'Esch</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22821,7 +22821,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Mondorf-les-Bains</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -22857,13 +22857,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M174" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -22896,16 +22896,16 @@
         <v>0</v>
       </c>
       <c r="Y174" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z174" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AA174" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB174" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC174" t="n">
         <v>0</v>
@@ -22950,7 +22950,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -22960,12 +22960,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23079,7 +23079,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23089,12 +23089,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Eléctrico</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23208,7 +23208,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23347,12 +23347,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23605,12 +23605,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23734,12 +23734,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Atlético Malveira</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23853,7 +23853,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23982,7 +23982,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -24111,7 +24111,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -24121,12 +24121,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Hércules CF</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24369,7 +24369,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>UNA Strassen</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Mamer</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24756,7 +24756,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -24766,12 +24766,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Atlético Malveira</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24895,12 +24895,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Naval 1º de Maio</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25014,7 +25014,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25024,12 +25024,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25143,7 +25143,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -25153,12 +25153,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25272,7 +25272,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25282,12 +25282,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25411,12 +25411,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -25530,7 +25530,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -25540,12 +25540,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -25566,13 +25566,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M195" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N195" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -25605,10 +25605,10 @@
         <v>0</v>
       </c>
       <c r="Y195" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z195" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA195" t="n">
         <v>0</v>
@@ -25659,7 +25659,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -25669,12 +25669,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -25788,7 +25788,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -25798,12 +25798,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Sanjoanense</t>
+          <t>Naval 1º de Maio</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26175,7 +26175,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Leça</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Clube Oriental de Lisboa</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26304,7 +26304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26314,12 +26314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Lusitano Évora 1911</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26433,7 +26433,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -26443,12 +26443,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26562,7 +26562,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -26572,12 +26572,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Clube Oriental de Lisboa</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26598,13 +26598,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M203" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N203" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -26637,16 +26637,16 @@
         <v>0</v>
       </c>
       <c r="Y203" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z203" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AA203" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB203" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC203" t="n">
         <v>0</v>
@@ -26701,12 +26701,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Eléctrico</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Leça</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26949,22 +26949,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27078,22 +27078,22 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27207,7 +27207,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -27217,12 +27217,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27336,22 +27336,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27465,7 +27465,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Sporting CP II</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27501,13 +27501,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M210" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N210" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -27540,10 +27540,10 @@
         <v>0</v>
       </c>
       <c r="Y210" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z210" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA210" t="n">
         <v>0</v>
@@ -27594,22 +27594,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27723,22 +27723,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27852,7 +27852,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -27862,12 +27862,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27981,7 +27981,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -27991,12 +27991,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28017,13 +28017,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M214" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N214" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -28056,10 +28056,10 @@
         <v>0</v>
       </c>
       <c r="Y214" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z214" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA214" t="n">
         <v>0</v>
@@ -28110,7 +28110,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28120,12 +28120,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28239,22 +28239,22 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28275,13 +28275,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N216" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -28314,10 +28314,10 @@
         <v>0</v>
       </c>
       <c r="Y216" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z216" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA216" t="n">
         <v>0</v>
@@ -28368,7 +28368,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -28378,12 +28378,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Sporting CP II</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -28497,7 +28497,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -28507,12 +28507,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -28533,13 +28533,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M218" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -28578,10 +28578,10 @@
         <v>0</v>
       </c>
       <c r="AA218" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB218" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC218" t="n">
         <v>0</v>
@@ -28626,7 +28626,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -28636,12 +28636,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -28662,13 +28662,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N219" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -28707,10 +28707,10 @@
         <v>0</v>
       </c>
       <c r="AA219" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB219" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC219" t="n">
         <v>0</v>
@@ -28755,7 +28755,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -28884,7 +28884,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -28894,12 +28894,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -28920,13 +28920,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M221" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="N221" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -28965,10 +28965,10 @@
         <v>0</v>
       </c>
       <c r="AA221" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB221" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC221" t="n">
         <v>0</v>
@@ -29013,7 +29013,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29049,13 +29049,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="N222" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -29094,10 +29094,10 @@
         <v>0</v>
       </c>
       <c r="AA222" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB222" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC222" t="n">
         <v>0</v>
@@ -29142,22 +29142,22 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29400,7 +29400,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -29410,12 +29410,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -29539,12 +29539,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Skalica</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>DAC</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29658,22 +29658,22 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -29797,12 +29797,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -29916,7 +29916,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -29926,12 +29926,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30045,7 +30045,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -30055,12 +30055,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30081,13 +30081,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M230" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N230" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -30120,10 +30120,10 @@
         <v>0</v>
       </c>
       <c r="Y230" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z230" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA230" t="n">
         <v>0</v>
@@ -30174,7 +30174,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -30184,12 +30184,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>LNZ Cherkasy</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30432,7 +30432,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -30442,12 +30442,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -30468,13 +30468,13 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M233" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N233" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -30507,10 +30507,10 @@
         <v>0</v>
       </c>
       <c r="Y233" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Z233" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA233" t="n">
         <v>0</v>
@@ -30561,7 +30561,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -30571,12 +30571,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Skalica</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>DAC</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -30690,7 +30690,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -30700,12 +30700,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30819,7 +30819,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -30829,12 +30829,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30948,7 +30948,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -30958,12 +30958,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -30984,13 +30984,13 @@
         </is>
       </c>
       <c r="L237" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M237" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="N237" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="O237" t="n">
         <v>0</v>
@@ -31023,10 +31023,10 @@
         <v>0</v>
       </c>
       <c r="Y237" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z237" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA237" t="n">
         <v>0</v>
@@ -31077,7 +31077,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -31087,12 +31087,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31206,22 +31206,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31335,22 +31335,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Haugesund</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31464,22 +31464,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>KFUM</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -31593,7 +31593,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -31603,12 +31603,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -31722,7 +31722,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -31732,12 +31732,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -31851,22 +31851,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Haugesund</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -31980,7 +31980,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -31990,12 +31990,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>LNZ Cherkasy</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32109,22 +32109,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>KFUM</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32238,7 +32238,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -32248,12 +32248,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32496,22 +32496,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32625,7 +32625,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -32635,12 +32635,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32754,7 +32754,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -32764,12 +32764,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -32883,7 +32883,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -32893,12 +32893,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -32919,13 +32919,13 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M252" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="N252" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O252" t="n">
         <v>0</v>
@@ -32958,10 +32958,10 @@
         <v>0</v>
       </c>
       <c r="Y252" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z252" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA252" t="n">
         <v>0</v>
@@ -33012,22 +33012,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33141,7 +33141,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -33151,12 +33151,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -33270,22 +33270,22 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33399,7 +33399,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -33409,12 +33409,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Nice</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33435,13 +33435,13 @@
         </is>
       </c>
       <c r="L256" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M256" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N256" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O256" t="n">
         <v>0</v>
@@ -33480,10 +33480,10 @@
         <v>0</v>
       </c>
       <c r="AA256" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB256" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC256" t="n">
         <v>0</v>
@@ -33538,12 +33538,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -33564,13 +33564,13 @@
         </is>
       </c>
       <c r="L257" t="n">
-        <v>3.15</v>
+        <v>1.62</v>
       </c>
       <c r="M257" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N257" t="n">
-        <v>2.25</v>
+        <v>5.4</v>
       </c>
       <c r="O257" t="n">
         <v>0</v>
@@ -33603,10 +33603,10 @@
         <v>0</v>
       </c>
       <c r="Y257" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="Z257" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AA257" t="n">
         <v>0</v>
@@ -33657,7 +33657,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -33667,12 +33667,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33693,13 +33693,13 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M258" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N258" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -33732,10 +33732,10 @@
         <v>0</v>
       </c>
       <c r="Y258" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z258" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA258" t="n">
         <v>0</v>
@@ -33822,13 +33822,13 @@
         </is>
       </c>
       <c r="L259" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M259" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N259" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O259" t="n">
         <v>0</v>
@@ -33925,12 +33925,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Nice</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -33951,13 +33951,13 @@
         </is>
       </c>
       <c r="L260" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="M260" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="N260" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="O260" t="n">
         <v>0</v>
@@ -33990,16 +33990,16 @@
         <v>0</v>
       </c>
       <c r="Y260" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z260" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA260" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB260" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC260" t="n">
         <v>0</v>
@@ -34173,7 +34173,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -34183,12 +34183,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34431,7 +34431,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -34441,12 +34441,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -34560,7 +34560,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -34570,12 +34570,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -34828,12 +34828,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -34947,7 +34947,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -34957,12 +34957,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -35205,22 +35205,22 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -35241,13 +35241,13 @@
         </is>
       </c>
       <c r="L270" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M270" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N270" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O270" t="n">
         <v>0</v>
@@ -35334,22 +35334,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -35370,13 +35370,13 @@
         </is>
       </c>
       <c r="L271" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M271" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N271" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O271" t="n">
         <v>0</v>
@@ -35463,7 +35463,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -35473,12 +35473,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -35592,7 +35592,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -35602,12 +35602,12 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -35721,7 +35721,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -35731,12 +35731,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -35850,7 +35850,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -35860,12 +35860,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -35979,7 +35979,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -35989,12 +35989,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -36108,7 +36108,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -36118,12 +36118,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -36144,13 +36144,13 @@
         </is>
       </c>
       <c r="L277" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M277" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N277" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O277" t="n">
         <v>0</v>
@@ -36183,10 +36183,10 @@
         <v>0</v>
       </c>
       <c r="Y277" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z277" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA277" t="n">
         <v>0</v>
@@ -36237,7 +36237,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -36247,12 +36247,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -36366,7 +36366,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -36376,12 +36376,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -36402,13 +36402,13 @@
         </is>
       </c>
       <c r="L279" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M279" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N279" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O279" t="n">
         <v>0</v>
@@ -36441,10 +36441,10 @@
         <v>0</v>
       </c>
       <c r="Y279" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z279" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA279" t="n">
         <v>0</v>
@@ -36624,7 +36624,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -36634,12 +36634,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -36753,7 +36753,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -36763,12 +36763,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Sporting Covilhã</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -36789,13 +36789,13 @@
         </is>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M282" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N282" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O282" t="n">
         <v>0</v>
@@ -36882,7 +36882,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -36892,12 +36892,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -37011,7 +37011,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -37021,12 +37021,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -37140,7 +37140,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -37150,12 +37150,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Sporting Covilhã</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -37398,7 +37398,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -37408,12 +37408,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -37537,12 +37537,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -37795,12 +37795,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -37914,22 +37914,22 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -38043,7 +38043,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -38053,12 +38053,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -38172,22 +38172,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -38301,7 +38301,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -38311,12 +38311,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -38430,7 +38430,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -38440,12 +38440,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -38559,7 +38559,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -38569,12 +38569,12 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -38817,7 +38817,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -38827,12 +38827,12 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -38946,22 +38946,22 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Omonia Nicosia</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>New York City II</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -38982,13 +38982,13 @@
         </is>
       </c>
       <c r="L299" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M299" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N299" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O299" t="n">
         <v>0</v>
@@ -39021,10 +39021,10 @@
         <v>0</v>
       </c>
       <c r="Y299" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z299" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA299" t="n">
         <v>0</v>
@@ -39075,7 +39075,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -39085,12 +39085,12 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -39204,22 +39204,22 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>New York City II</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -39462,22 +39462,22 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -39591,22 +39591,22 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -39730,12 +39730,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Atlanta United II</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -39849,22 +39849,22 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -39885,13 +39885,13 @@
         </is>
       </c>
       <c r="L306" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M306" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N306" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O306" t="n">
         <v>0</v>
@@ -39924,10 +39924,10 @@
         <v>0</v>
       </c>
       <c r="Y306" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z306" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA306" t="n">
         <v>0</v>
@@ -39978,7 +39978,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -39988,12 +39988,12 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -40107,22 +40107,22 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -40236,22 +40236,22 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Omonia Nicosia</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -40272,13 +40272,13 @@
         </is>
       </c>
       <c r="L309" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M309" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N309" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O309" t="n">
         <v>0</v>
@@ -40311,10 +40311,10 @@
         <v>0</v>
       </c>
       <c r="Y309" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z309" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA309" t="n">
         <v>0</v>
@@ -40365,7 +40365,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -40375,12 +40375,12 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -40494,7 +40494,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -40504,12 +40504,12 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -40530,13 +40530,13 @@
         </is>
       </c>
       <c r="L311" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M311" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N311" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O311" t="n">
         <v>0</v>
@@ -40563,10 +40563,10 @@
         <v>0</v>
       </c>
       <c r="W311" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X311" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y311" t="n">
         <v>0</v>
@@ -40623,22 +40623,22 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -40752,22 +40752,22 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -40881,22 +40881,22 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Atlanta United II</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -41268,7 +41268,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -41278,12 +41278,12 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -41304,13 +41304,13 @@
         </is>
       </c>
       <c r="L317" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="M317" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="N317" t="n">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="O317" t="n">
         <v>0</v>
@@ -41343,10 +41343,10 @@
         <v>0</v>
       </c>
       <c r="Y317" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="Z317" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="AA317" t="n">
         <v>0</v>
@@ -41397,7 +41397,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -41407,12 +41407,12 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="G318" t="n">
@@ -41433,13 +41433,13 @@
         </is>
       </c>
       <c r="L318" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M318" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N318" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O318" t="n">
         <v>0</v>
@@ -41472,10 +41472,10 @@
         <v>0</v>
       </c>
       <c r="Y318" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Z318" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA318" t="n">
         <v>0</v>
@@ -41526,7 +41526,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -41536,12 +41536,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -41562,13 +41562,13 @@
         </is>
       </c>
       <c r="L319" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M319" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N319" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O319" t="n">
         <v>0</v>
@@ -41601,10 +41601,10 @@
         <v>0</v>
       </c>
       <c r="Y319" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Z319" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA319" t="n">
         <v>0</v>
@@ -41655,7 +41655,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -41665,12 +41665,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G320" t="n">
@@ -41784,7 +41784,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -41794,12 +41794,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="G321" t="n">
@@ -41820,13 +41820,13 @@
         </is>
       </c>
       <c r="L321" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M321" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N321" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O321" t="n">
         <v>0</v>
@@ -41859,10 +41859,10 @@
         <v>0</v>
       </c>
       <c r="Y321" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z321" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA321" t="n">
         <v>0</v>
@@ -41913,7 +41913,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -41923,12 +41923,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -41949,13 +41949,13 @@
         </is>
       </c>
       <c r="L322" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M322" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N322" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O322" t="n">
         <v>0</v>
@@ -41988,10 +41988,10 @@
         <v>0</v>
       </c>
       <c r="Y322" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z322" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA322" t="n">
         <v>0</v>
@@ -42052,12 +42052,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Santiago Morning</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G323" t="n">
@@ -42081,10 +42081,10 @@
         <v>2.63</v>
       </c>
       <c r="M323" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N323" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="O323" t="n">
         <v>0</v>
@@ -42171,22 +42171,22 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G324" t="n">
@@ -42207,13 +42207,13 @@
         </is>
       </c>
       <c r="L324" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M324" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N324" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O324" t="n">
         <v>0</v>
@@ -42300,22 +42300,22 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Santiago Morning</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -42336,13 +42336,13 @@
         </is>
       </c>
       <c r="L325" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M325" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N325" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O325" t="n">
         <v>0</v>
@@ -42558,7 +42558,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -42568,12 +42568,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G327" t="n">
@@ -42687,7 +42687,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -42697,12 +42697,12 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G328" t="n">
@@ -42945,7 +42945,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -42955,12 +42955,12 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="G330" t="n">
@@ -43074,7 +43074,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -43084,12 +43084,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="G331" t="n">
@@ -43203,7 +43203,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -43213,12 +43213,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G332" t="n">
@@ -43590,22 +43590,22 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Tusker</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Shabana</t>
         </is>
       </c>
       <c r="G335" t="n">
@@ -43719,7 +43719,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -43729,12 +43729,12 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G336" t="n">
@@ -43848,7 +43848,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -43858,12 +43858,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Valour FC</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G337" t="n">
@@ -43977,7 +43977,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -43987,12 +43987,12 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Tusker</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Shabana</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G338" t="n">
@@ -44106,7 +44106,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -44116,12 +44116,12 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G339" t="n">
@@ -44364,7 +44364,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -44374,12 +44374,12 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Valour FC</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G341" t="n">
@@ -44493,22 +44493,22 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G342" t="n">
@@ -44632,12 +44632,12 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G343" t="n">
@@ -44761,12 +44761,12 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G344" t="n">
@@ -44880,7 +44880,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -44890,12 +44890,12 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="G345" t="n">
@@ -45019,12 +45019,12 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G346" t="n">
@@ -45148,12 +45148,12 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Tacoma Defiance</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G347" t="n">
@@ -45277,12 +45277,12 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Tacoma Defiance</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G348" t="n">
@@ -45525,7 +45525,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -45535,12 +45535,12 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>LA Galaxy II</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G350" t="n">
@@ -45654,7 +45654,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -45664,12 +45664,12 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G351" t="n">
@@ -45783,7 +45783,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -45793,12 +45793,12 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G352" t="n">
@@ -45922,12 +45922,12 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>LA Galaxy II</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G353" t="n">
@@ -46051,12 +46051,12 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G354" t="n">
@@ -46180,12 +46180,12 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G355" t="n">
@@ -46309,12 +46309,12 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G356" t="n">
@@ -46428,22 +46428,22 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G357" t="n">
@@ -46464,13 +46464,13 @@
         </is>
       </c>
       <c r="L357" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M357" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N357" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O357" t="n">
         <v>0</v>
@@ -46503,10 +46503,10 @@
         <v>0</v>
       </c>
       <c r="Y357" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z357" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA357" t="n">
         <v>0</v>
@@ -46567,12 +46567,12 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G358" t="n">
@@ -46686,22 +46686,22 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G359" t="n">
@@ -46722,13 +46722,13 @@
         </is>
       </c>
       <c r="L359" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M359" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N359" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O359" t="n">
         <v>0</v>
@@ -46761,10 +46761,10 @@
         <v>0</v>
       </c>
       <c r="Y359" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z359" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA359" t="n">
         <v>0</v>
@@ -46825,12 +46825,12 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G360" t="n">
@@ -47589,7 +47589,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -47599,12 +47599,12 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G366" t="n">
@@ -47718,7 +47718,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -47728,12 +47728,12 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G367" t="n">
@@ -48100,7 +48100,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -48220,7 +48220,7 @@
         <v>0</v>
       </c>
       <c r="AK370" s="3" t="n">
-        <v>45935.97916666666</v>
+        <v>45935.91666666666</v>
       </c>
     </row>
   </sheetData>
